--- a/Data/dissection.xlsx
+++ b/Data/dissection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivancasas/GitHub/EIP/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivancasas/GitHub/Survival/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A201A5-F150-D84C-950B-CB2A32F68D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB6F8BD-3967-2646-B396-F8821F42B374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{15397DBD-5D50-3349-8532-24EF1C547B02}"/>
+    <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{15397DBD-5D50-3349-8532-24EF1C547B02}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -500,7 +500,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE4B7C3-6EEC-3E40-A639-037475DFAEB6}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S1226"/>
+  <dimension ref="A1:S1128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5244,7 +5244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="str">
         <f>A119</f>
         <v>r04</v>
@@ -19253,7 +19253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A471" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19293,7 +19293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19333,7 +19333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19373,7 +19373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19893,7 +19893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A487" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19933,7 +19933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19973,7 +19973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20013,7 +20013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20533,7 +20533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A503" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20573,7 +20573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A504" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20613,7 +20613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A505" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20653,7 +20653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A506" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21173,7 +21173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A519" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21213,7 +21213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A520" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21253,7 +21253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A521" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21293,7 +21293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21813,7 +21813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21853,7 +21853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21893,7 +21893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21933,7 +21933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22453,7 +22453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22493,7 +22493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22533,7 +22533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22573,7 +22573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A554" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23093,7 +23093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23133,7 +23133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23173,7 +23173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A569" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23213,7 +23213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23733,7 +23733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A583" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23773,7 +23773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A584" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23813,7 +23813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A585" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23853,7 +23853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A586" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -24373,7 +24373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24404,16 +24404,16 @@
         <v>2</v>
       </c>
       <c r="I599">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J599">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K599">
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A600" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24444,16 +24444,16 @@
         <v>2</v>
       </c>
       <c r="I600">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J600">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K600">
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24484,16 +24484,16 @@
         <v>2</v>
       </c>
       <c r="I601">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J601">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K601">
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24524,10 +24524,10 @@
         <v>2</v>
       </c>
       <c r="I602">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J602">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K602">
         <v>0</v>
@@ -25013,7 +25013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A615" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25053,7 +25053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A616" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25093,7 +25093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A617" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25133,7 +25133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A618" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25653,7 +25653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A631" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25693,7 +25693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25733,7 +25733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25773,7 +25773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -30550,7 +30550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -38428,7 +38428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A947" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38469,7 +38469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A948" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -41145,7 +41145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1010" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -42529,7 +42529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1041" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1041" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -46089,7 +46089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1121" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1121" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46129,7 +46129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1122" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1122" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46169,7 +46169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1123" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1123" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46215,7 +46215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1124" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1124" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46261,7 +46261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1125" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1125" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46307,7 +46307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1126" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1126" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46353,7 +46353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1127" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1127" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46399,7 +46399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1128" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A1128" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46445,330 +46445,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1129" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1129" s="1"/>
-      <c r="M1129" s="2"/>
-    </row>
-    <row r="1130" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1130" s="1"/>
-    </row>
-    <row r="1131" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1131" s="1"/>
-    </row>
-    <row r="1132" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1132" s="1"/>
-    </row>
-    <row r="1133" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1133" s="1"/>
-      <c r="N1133" s="2"/>
-    </row>
-    <row r="1134" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1134" s="1"/>
-    </row>
-    <row r="1135" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1135" s="1"/>
-    </row>
-    <row r="1136" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C1136" s="1"/>
-    </row>
-    <row r="1137" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1137" s="1"/>
-    </row>
-    <row r="1138" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1138" s="1"/>
-    </row>
-    <row r="1139" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1139" s="1"/>
-    </row>
-    <row r="1140" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1140" s="1"/>
-    </row>
-    <row r="1141" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1141" s="1"/>
-    </row>
-    <row r="1142" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1142" s="1"/>
-    </row>
-    <row r="1143" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1143" s="1"/>
-    </row>
-    <row r="1144" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1144" s="1"/>
-    </row>
-    <row r="1145" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1145" s="1"/>
-    </row>
-    <row r="1146" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1146" s="1"/>
-    </row>
-    <row r="1147" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1147" s="1"/>
-    </row>
-    <row r="1148" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1148" s="1"/>
-    </row>
-    <row r="1149" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1149" s="1"/>
-    </row>
-    <row r="1150" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1150" s="1"/>
-    </row>
-    <row r="1151" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1151" s="1"/>
-    </row>
-    <row r="1152" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1152" s="1"/>
-    </row>
-    <row r="1153" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1153" s="1"/>
-    </row>
-    <row r="1154" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1154" s="1"/>
-    </row>
-    <row r="1155" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1155" s="1"/>
-    </row>
-    <row r="1156" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1156" s="1"/>
-    </row>
-    <row r="1157" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1157" s="1"/>
-    </row>
-    <row r="1158" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1158" s="1"/>
-    </row>
-    <row r="1159" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1159" s="1"/>
-    </row>
-    <row r="1160" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1160" s="1"/>
-    </row>
-    <row r="1161" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1161" s="1"/>
-    </row>
-    <row r="1162" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1162" s="1"/>
-    </row>
-    <row r="1163" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1163" s="1"/>
-    </row>
-    <row r="1164" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1164" s="1"/>
-    </row>
-    <row r="1165" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1165" s="1"/>
-    </row>
-    <row r="1166" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1166" s="1"/>
-    </row>
-    <row r="1167" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1167" s="1"/>
-    </row>
-    <row r="1168" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1168" s="1"/>
-    </row>
-    <row r="1169" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1169" s="1"/>
-    </row>
-    <row r="1170" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1170" s="1"/>
-    </row>
-    <row r="1171" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1171" s="1"/>
-    </row>
-    <row r="1172" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1172" s="1"/>
-    </row>
-    <row r="1173" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1173" s="1"/>
-    </row>
-    <row r="1174" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1174" s="1"/>
-    </row>
-    <row r="1175" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1175" s="1"/>
-    </row>
-    <row r="1176" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1176" s="1"/>
-    </row>
-    <row r="1177" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1177" s="1"/>
-    </row>
-    <row r="1178" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1178" s="1"/>
-    </row>
-    <row r="1179" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1179" s="1"/>
-    </row>
-    <row r="1180" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1180" s="1"/>
-    </row>
-    <row r="1181" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1181" s="1"/>
-    </row>
-    <row r="1182" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1182" s="1"/>
-    </row>
-    <row r="1183" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1183" s="1"/>
-    </row>
-    <row r="1184" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1184" s="1"/>
-    </row>
-    <row r="1185" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1185" s="1"/>
-    </row>
-    <row r="1186" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1186" s="1"/>
-    </row>
-    <row r="1187" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1187" s="1"/>
-    </row>
-    <row r="1188" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1188" s="1"/>
-    </row>
-    <row r="1189" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1189" s="1"/>
-    </row>
-    <row r="1190" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1190" s="1"/>
-    </row>
-    <row r="1191" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1191" s="1"/>
-    </row>
-    <row r="1192" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1192" s="1"/>
-    </row>
-    <row r="1193" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1193" s="1"/>
-    </row>
-    <row r="1194" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1194" s="1"/>
-    </row>
-    <row r="1195" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1195" s="1"/>
-    </row>
-    <row r="1196" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1196" s="1"/>
-    </row>
-    <row r="1197" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1197" s="1"/>
-    </row>
-    <row r="1198" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1198" s="1"/>
-    </row>
-    <row r="1199" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1199" s="1"/>
-    </row>
-    <row r="1200" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1200" s="1"/>
-    </row>
-    <row r="1201" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1201" s="1"/>
-    </row>
-    <row r="1202" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1202" s="1"/>
-    </row>
-    <row r="1203" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1203" s="1"/>
-    </row>
-    <row r="1204" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1204" s="1"/>
-    </row>
-    <row r="1205" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1205" s="1"/>
-    </row>
-    <row r="1206" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1206" s="1"/>
-    </row>
-    <row r="1207" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1207" s="1"/>
-    </row>
-    <row r="1208" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1208" s="1"/>
-    </row>
-    <row r="1209" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1209" s="1"/>
-    </row>
-    <row r="1210" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1210" s="1"/>
-    </row>
-    <row r="1211" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1211" s="1"/>
-    </row>
-    <row r="1212" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1212" s="1"/>
-    </row>
-    <row r="1213" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1213" s="1"/>
-    </row>
-    <row r="1214" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1214" s="1"/>
-    </row>
-    <row r="1215" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1215" s="1"/>
-    </row>
-    <row r="1216" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1216" s="1"/>
-    </row>
-    <row r="1217" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1217" s="1"/>
-    </row>
-    <row r="1218" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1218" s="1"/>
-    </row>
-    <row r="1219" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1219" s="1"/>
-    </row>
-    <row r="1220" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1220" s="1"/>
-    </row>
-    <row r="1221" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1221" s="1"/>
-    </row>
-    <row r="1222" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1222" s="1"/>
-    </row>
-    <row r="1223" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1223" s="1"/>
-    </row>
-    <row r="1224" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1224" s="1"/>
-    </row>
-    <row r="1225" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1225" s="1"/>
-    </row>
-    <row r="1226" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C1226" s="1"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:K1128" xr:uid="{9EE4B7C3-6EEC-3E40-A639-037475DFAEB6}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="r07"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3">
       <filters>
-        <filter val="ki276"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="1"/>
-        <filter val="13"/>
-        <filter val="19"/>
-        <filter val="2"/>
-        <filter val="27"/>
-        <filter val="3"/>
-        <filter val="32"/>
-        <filter val="33"/>
-        <filter val="38"/>
-        <filter val="4"/>
-        <filter val="43"/>
-        <filter val="45"/>
-        <filter val="46"/>
-        <filter val="49"/>
-        <filter val="55"/>
-        <filter val="6"/>
-        <filter val="67"/>
-        <filter val="8"/>
-        <filter val="9"/>
+        <filter val="ci216"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Data/dissection.xlsx
+++ b/Data/dissection.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivancasas/GitHub/Survival/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ivancasas/GitHub/temp-RISK/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB6F8BD-3967-2646-B396-F8821F42B374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA238B8-3A0E-F843-BFEF-00BB5CDC89E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{15397DBD-5D50-3349-8532-24EF1C547B02}"/>
   </bookViews>
@@ -120,7 +120,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -133,12 +133,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Helvetica"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,10 +155,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,8 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE4B7C3-6EEC-3E40-A639-037475DFAEB6}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:S1128"/>
+  <dimension ref="A1:K1128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -550,7 +542,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -585,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>A2</f>
         <v>r04</v>
@@ -624,7 +616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f t="shared" ref="A4:A67" si="0">A3</f>
         <v>r04</v>
@@ -663,7 +655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -702,7 +694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -741,7 +733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -780,7 +772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -818,7 +810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -857,7 +849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -896,7 +888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -935,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -973,7 +965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1012,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1051,7 +1043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1090,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1129,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1168,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1206,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1245,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1284,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1323,7 +1315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1363,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1403,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1443,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1483,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1523,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1563,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1603,7 +1595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1643,7 +1635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1683,7 +1675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1723,7 +1715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1763,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1803,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1843,7 +1835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1883,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1923,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -1963,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2003,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2043,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2083,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2123,7 +2115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2163,7 +2155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2203,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2243,7 +2235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2283,7 +2275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2323,7 +2315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2363,7 +2355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2403,7 +2395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2443,7 +2435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2483,7 +2475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2523,7 +2515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2563,7 +2555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2603,7 +2595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2643,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2683,7 +2675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2723,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2763,7 +2755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2803,7 +2795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2843,7 +2835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2883,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2923,7 +2915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -2963,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -3003,7 +2995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -3043,7 +3035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -3083,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -3123,7 +3115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" t="str">
         <f t="shared" si="0"/>
         <v>r04</v>
@@ -3163,7 +3155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" t="str">
         <f t="shared" ref="A68:A123" si="14">A67</f>
         <v>r04</v>
@@ -3203,7 +3195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3243,7 +3235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3283,7 +3275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3323,7 +3315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3363,7 +3355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3403,7 +3395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3443,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3483,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3523,7 +3515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3563,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3603,7 +3595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3643,7 +3635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3683,7 +3675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3723,7 +3715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3763,7 +3755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3803,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3843,7 +3835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3883,7 +3875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3923,7 +3915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -3963,7 +3955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4003,7 +3995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4043,7 +4035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4083,7 +4075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4123,7 +4115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4163,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4202,9 +4194,8 @@
       <c r="K93">
         <v>0</v>
       </c>
-      <c r="S93" s="2"/>
-    </row>
-    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4244,7 +4235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4284,7 +4275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4324,7 +4315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4364,7 +4355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4404,7 +4395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4444,7 +4435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4484,7 +4475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4524,7 +4515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4564,7 +4555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4604,7 +4595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4644,7 +4635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4684,7 +4675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A106" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4724,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4764,7 +4755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4804,7 +4795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A109" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4844,7 +4835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4884,7 +4875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4924,7 +4915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -4964,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5004,7 +4995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5044,7 +5035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5084,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5124,7 +5115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5164,7 +5155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5204,7 +5195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5244,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" t="str">
         <f>A119</f>
         <v>r04</v>
@@ -5284,7 +5275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5324,7 +5315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5364,7 +5355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" t="str">
         <f t="shared" si="14"/>
         <v>r04</v>
@@ -5404,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -5439,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" t="str">
         <f>A124</f>
         <v>r05</v>
@@ -5477,7 +5468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" t="str">
         <f t="shared" ref="A126:A189" si="57">A125</f>
         <v>r05</v>
@@ -5516,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5555,7 +5546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5594,7 +5585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5633,7 +5624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5673,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5713,7 +5704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5753,7 +5744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5793,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5833,7 +5824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5872,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5912,7 +5903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5952,7 +5943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -5992,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6032,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6072,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6112,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6152,7 +6143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6192,7 +6183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6232,7 +6223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6272,7 +6263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6312,7 +6303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6352,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6392,7 +6383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6432,7 +6423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6472,7 +6463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6512,7 +6503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6552,7 +6543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6592,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6632,7 +6623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6671,7 +6662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6710,7 +6701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6749,7 +6740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6788,7 +6779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6828,7 +6819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6868,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6908,7 +6899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6947,7 +6938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -6987,7 +6978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7027,7 +7018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7067,7 +7058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7107,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7147,7 +7138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7187,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7227,7 +7218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7267,7 +7258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7307,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7347,7 +7338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7387,7 +7378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7427,7 +7418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7467,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7507,7 +7498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7547,7 +7538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7587,7 +7578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7627,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7667,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7707,7 +7698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7747,7 +7738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7787,7 +7778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7827,7 +7818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7867,7 +7858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7907,7 +7898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7947,7 +7938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -7987,7 +7978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" t="str">
         <f t="shared" si="57"/>
         <v>r05</v>
@@ -8027,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" t="str">
         <f t="shared" ref="A190:A234" si="120">A189</f>
         <v>r05</v>
@@ -8067,7 +8058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8107,7 +8098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8147,7 +8138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8187,7 +8178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8227,7 +8218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8267,7 +8258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8307,7 +8298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8347,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8387,7 +8378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8427,7 +8418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8467,7 +8458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8507,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8547,7 +8538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8587,7 +8578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8627,7 +8618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8667,7 +8658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8707,7 +8698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8747,7 +8738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8787,7 +8778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8827,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8867,7 +8858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8907,7 +8898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8947,7 +8938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -8987,7 +8978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9027,7 +9018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9067,7 +9058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9107,7 +9098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9147,7 +9138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9187,7 +9178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9227,7 +9218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9267,7 +9258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9307,7 +9298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9347,7 +9338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9387,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9427,7 +9418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9467,7 +9458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9507,7 +9498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9547,7 +9538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9587,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9627,7 +9618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9667,7 +9658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9707,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9747,7 +9738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9787,7 +9778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" t="str">
         <f t="shared" si="120"/>
         <v>r05</v>
@@ -9827,7 +9818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>20</v>
       </c>
@@ -9862,7 +9853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" t="str">
         <f>A235</f>
         <v>r06</v>
@@ -9901,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" t="str">
         <f t="shared" ref="A237:A300" si="203">A236</f>
         <v>r06</v>
@@ -9940,7 +9931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -9979,7 +9970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10018,7 +10009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10058,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10098,7 +10089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10138,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10177,7 +10168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10217,7 +10208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10257,7 +10248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10297,7 +10288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10336,7 +10327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10376,7 +10367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10416,7 +10407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10456,7 +10447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10496,7 +10487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10536,7 +10527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10576,7 +10567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10616,7 +10607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10656,7 +10647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10696,7 +10687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10736,7 +10727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10776,7 +10767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10816,7 +10807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10856,7 +10847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10896,7 +10887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10936,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -10976,7 +10967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11016,7 +11007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11056,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11096,7 +11087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11136,7 +11127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11176,7 +11167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11216,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11256,7 +11247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11296,7 +11287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11336,7 +11327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11376,7 +11367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11416,7 +11407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11456,7 +11447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11496,7 +11487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11536,7 +11527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11576,7 +11567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11616,7 +11607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11656,7 +11647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11696,7 +11687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11736,7 +11727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11776,7 +11767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11816,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11856,7 +11847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11896,7 +11887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11936,7 +11927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -11976,7 +11967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12016,7 +12007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12056,7 +12047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12096,7 +12087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12136,7 +12127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12176,7 +12167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12216,7 +12207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12256,7 +12247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12296,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12336,7 +12327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12376,7 +12367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12416,7 +12407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" t="str">
         <f t="shared" si="203"/>
         <v>r06</v>
@@ -12456,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" t="str">
         <f t="shared" ref="A301:A364" si="305">A300</f>
         <v>r06</v>
@@ -12496,7 +12487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12536,7 +12527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12576,7 +12567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12616,7 +12607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12656,7 +12647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12696,7 +12687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12736,7 +12727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12776,7 +12767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12816,7 +12807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12856,7 +12847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12896,7 +12887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12936,7 +12927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -12976,7 +12967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13016,7 +13007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13056,7 +13047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13096,7 +13087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13136,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13176,7 +13167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13216,7 +13207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13256,7 +13247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13296,7 +13287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13336,7 +13327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13376,7 +13367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13416,7 +13407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13456,7 +13447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13496,7 +13487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13536,7 +13527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13576,7 +13567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13616,7 +13607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13656,7 +13647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13696,7 +13687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13736,7 +13727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13776,7 +13767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13816,7 +13807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13856,7 +13847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13896,7 +13887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13936,7 +13927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -13976,7 +13967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14016,7 +14007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14056,7 +14047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14096,7 +14087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14136,7 +14127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14176,7 +14167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14216,7 +14207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14256,7 +14247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14296,7 +14287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14336,7 +14327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14376,7 +14367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14416,7 +14407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14456,7 +14447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14496,7 +14487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14536,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14576,7 +14567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14616,7 +14607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14656,7 +14647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14696,7 +14687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14736,7 +14727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14776,7 +14767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14816,7 +14807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14856,7 +14847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14896,7 +14887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14936,7 +14927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -14976,7 +14967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" t="str">
         <f t="shared" si="305"/>
         <v>r06</v>
@@ -15016,7 +15007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" t="str">
         <f t="shared" ref="A365:A428" si="434">A364</f>
         <v>r06</v>
@@ -15056,7 +15047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15096,7 +15087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15136,7 +15127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15176,7 +15167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15216,7 +15207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15256,7 +15247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15296,7 +15287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15336,7 +15327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15376,7 +15367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15416,7 +15407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15456,7 +15447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15496,7 +15487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15536,7 +15527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15576,7 +15567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15616,7 +15607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15656,7 +15647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15696,7 +15687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15736,7 +15727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15776,7 +15767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15816,7 +15807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15856,7 +15847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15896,7 +15887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15936,7 +15927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -15976,7 +15967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16016,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16056,7 +16047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16096,7 +16087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16136,7 +16127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16176,7 +16167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16216,7 +16207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16256,7 +16247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16296,7 +16287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16336,7 +16327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16376,7 +16367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16416,7 +16407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16456,7 +16447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16496,7 +16487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16536,7 +16527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16576,7 +16567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16616,7 +16607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16656,7 +16647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16696,7 +16687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16736,7 +16727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16776,7 +16767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16816,7 +16807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16856,7 +16847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16896,7 +16887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16936,7 +16927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -16976,7 +16967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17016,7 +17007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17056,7 +17047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17096,7 +17087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17136,7 +17127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17176,7 +17167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17216,7 +17207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17256,7 +17247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17296,7 +17287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17336,7 +17327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17376,7 +17367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17416,7 +17407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17456,7 +17447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17496,7 +17487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17536,7 +17527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" t="str">
         <f t="shared" si="434"/>
         <v>r06</v>
@@ -17576,7 +17567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" t="str">
         <f t="shared" ref="A429:A458" si="545">A428</f>
         <v>r06</v>
@@ -17616,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17656,7 +17647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17696,7 +17687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17736,7 +17727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17776,7 +17767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17816,7 +17807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A435" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17856,7 +17847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A436" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17896,7 +17887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A437" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17936,7 +17927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A438" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -17976,7 +17967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A439" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18016,7 +18007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A440" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18056,7 +18047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A441" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18096,7 +18087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A442" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18136,7 +18127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A443" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18176,7 +18167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A444" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18216,7 +18207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A445" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18256,7 +18247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A446" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18296,7 +18287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A447" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18336,7 +18327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A448" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18376,7 +18367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A449" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18416,7 +18407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A450" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18456,7 +18447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A451" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18496,7 +18487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18536,7 +18527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18576,7 +18567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18616,7 +18607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18656,7 +18647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A456" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18696,7 +18687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A457" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18736,7 +18727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A458" t="str">
         <f t="shared" si="545"/>
         <v>r06</v>
@@ -18776,7 +18767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>22</v>
       </c>
@@ -18813,7 +18804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A460" t="str">
         <f>A459</f>
         <v>r07</v>
@@ -18853,7 +18844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A461" t="str">
         <f t="shared" ref="A461:A524" si="579">A460</f>
         <v>r07</v>
@@ -18893,7 +18884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A462" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -18933,7 +18924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A463" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -18973,7 +18964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A464" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19013,7 +19004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A465" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19053,7 +19044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A466" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19093,7 +19084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A467" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19133,7 +19124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19173,7 +19164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19213,7 +19204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19413,7 +19404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A475" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19453,7 +19444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19493,7 +19484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19533,7 +19524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19573,7 +19564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A479" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19613,7 +19604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19653,7 +19644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19693,7 +19684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19733,7 +19724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19773,7 +19764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19813,7 +19804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -19853,7 +19844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20053,7 +20044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A491" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20093,7 +20084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20133,7 +20124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20173,7 +20164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20213,7 +20204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20253,7 +20244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20293,7 +20284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20333,7 +20324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20373,7 +20364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20413,7 +20404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20453,7 +20444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20493,7 +20484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A502" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20693,7 +20684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A507" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20733,7 +20724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A508" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20773,7 +20764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A509" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20813,7 +20804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A510" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20853,7 +20844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A511" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20893,7 +20884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A512" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20933,7 +20924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A513" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -20973,7 +20964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A514" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21013,7 +21004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A515" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21053,7 +21044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A516" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21093,7 +21084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A517" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21133,7 +21124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A518" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21333,7 +21324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21373,7 +21364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A524" t="str">
         <f t="shared" si="579"/>
         <v>r07</v>
@@ -21413,7 +21404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A525" t="str">
         <f t="shared" ref="A525:A588" si="681">A524</f>
         <v>r07</v>
@@ -21453,7 +21444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A526" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21493,7 +21484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21533,7 +21524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21573,7 +21564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21613,7 +21604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21653,7 +21644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21693,7 +21684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21733,7 +21724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21773,7 +21764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A534" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -21973,7 +21964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22013,7 +22004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22053,7 +22044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22093,7 +22084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22133,7 +22124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22173,7 +22164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22213,7 +22204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22253,7 +22244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A546" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22293,7 +22284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22333,7 +22324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22373,7 +22364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22413,7 +22404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A550" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22613,7 +22604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22653,7 +22644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22693,7 +22684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22733,7 +22724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22773,7 +22764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22813,7 +22804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22853,7 +22844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22893,7 +22884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22933,7 +22924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -22973,7 +22964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A564" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23013,7 +23004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23053,7 +23044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23253,7 +23244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23293,7 +23284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23333,7 +23324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A573" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23373,7 +23364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A574" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23413,7 +23404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A575" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23453,7 +23444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A576" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23493,7 +23484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A577" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23533,7 +23524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A578" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23573,7 +23564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A579" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23613,7 +23604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A580" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23653,7 +23644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A581" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23693,7 +23684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A582" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23893,7 +23884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A587" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23933,7 +23924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A588" t="str">
         <f t="shared" si="681"/>
         <v>r07</v>
@@ -23973,7 +23964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A589" t="str">
         <f t="shared" ref="A589:A634" si="809">A588</f>
         <v>r07</v>
@@ -24013,7 +24004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A590" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24053,7 +24044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A591" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24093,7 +24084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A592" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24133,7 +24124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A593" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24173,7 +24164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A594" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24213,7 +24204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A595" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24253,7 +24244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A596" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24293,7 +24284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24333,7 +24324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24533,7 +24524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24573,7 +24564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24613,7 +24604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A605" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24653,7 +24644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A606" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24693,7 +24684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A607" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24733,7 +24724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A608" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24773,7 +24764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A609" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24813,7 +24804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A610" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24853,7 +24844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A611" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24893,7 +24884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A612" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24933,7 +24924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A613" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -24973,7 +24964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A614" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25173,7 +25164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A619" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25213,7 +25204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A620" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25253,7 +25244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A621" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25293,7 +25284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A622" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25333,7 +25324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25373,7 +25364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25413,7 +25404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25453,7 +25444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25493,7 +25484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25533,7 +25524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25573,7 +25564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25613,7 +25604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630" t="str">
         <f t="shared" si="809"/>
         <v>r07</v>
@@ -25813,7 +25804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>23</v>
       </c>
@@ -25848,7 +25839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636" t="str">
         <f>A635</f>
         <v>r08</v>
@@ -25887,7 +25878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637" t="str">
         <f t="shared" ref="A637:A700" si="901">A636</f>
         <v>r08</v>
@@ -25926,7 +25917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -25965,7 +25956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A639" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26004,7 +25995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A640" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26043,7 +26034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A641" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26082,7 +26073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A642" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26121,7 +26112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A643" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26159,7 +26150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A644" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26198,7 +26189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A645" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26237,7 +26228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A646" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26276,7 +26267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A647" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26314,7 +26305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A648" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26353,7 +26344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A649" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26392,7 +26383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A650" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26431,7 +26422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A651" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26471,7 +26462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A652" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26511,7 +26502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A653" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26551,7 +26542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A654" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26591,7 +26582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A655" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26631,7 +26622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A656" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26671,7 +26662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A657" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26711,7 +26702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A658" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26751,7 +26742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A659" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26791,7 +26782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A660" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26831,7 +26822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A661" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26871,7 +26862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A662" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26911,7 +26902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A663" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26951,7 +26942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A664" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -26991,7 +26982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A665" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27031,7 +27022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A666" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27071,7 +27062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A667" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27111,7 +27102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A668" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27151,7 +27142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A669" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27191,7 +27182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="670" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A670" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27231,7 +27222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A671" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27271,7 +27262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A672" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27311,7 +27302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A673" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27351,7 +27342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A674" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27391,7 +27382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A675" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27431,7 +27422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A676" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27471,7 +27462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A677" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27511,7 +27502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A678" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27551,7 +27542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A679" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27591,7 +27582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A680" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27631,7 +27622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A681" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27671,7 +27662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27711,7 +27702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27751,7 +27742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27791,7 +27782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27831,7 +27822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27871,7 +27862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A687" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27911,7 +27902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A688" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27951,7 +27942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A689" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -27991,7 +27982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A690" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28031,7 +28022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A691" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28071,7 +28062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A692" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28111,7 +28102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A693" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28150,7 +28141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A694" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28190,7 +28181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A695" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28230,7 +28221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A696" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28270,7 +28261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A697" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28310,7 +28301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A698" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28350,7 +28341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A699" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28390,7 +28381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="700" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A700" t="str">
         <f t="shared" si="901"/>
         <v>r08</v>
@@ -28430,7 +28421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A701" t="str">
         <f t="shared" ref="A701:A765" si="976">A700</f>
         <v>r08</v>
@@ -28470,7 +28461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28510,7 +28501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28550,7 +28541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28590,7 +28581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28630,7 +28621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="706" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28670,7 +28661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28710,7 +28701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28750,7 +28741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A709" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28790,7 +28781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A710" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28830,7 +28821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A711" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28870,7 +28861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A712" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28910,7 +28901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A713" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28950,7 +28941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A714" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -28990,7 +28981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A715" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29030,7 +29021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A716" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29070,7 +29061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A717" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29110,7 +29101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A718" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29150,7 +29141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A719" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29190,7 +29181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A720" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29230,7 +29221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A721" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29270,7 +29261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A722" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29310,7 +29301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A723" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29350,7 +29341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A724" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29390,7 +29381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A725" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29430,7 +29421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="726" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A726" t="str">
         <f>A725</f>
         <v>r08</v>
@@ -29470,7 +29461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="727" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A727" t="str">
         <f>A725</f>
         <v>r08</v>
@@ -29510,7 +29501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A728" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29550,7 +29541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="729" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A729" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29590,7 +29581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A730" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29630,7 +29621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A731" t="str">
         <f>A730</f>
         <v>r08</v>
@@ -29670,7 +29661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:11" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:11" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29710,7 +29701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A733" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29750,7 +29741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A734" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29790,7 +29781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A735" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29830,7 +29821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A736" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29870,7 +29861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="737" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A737" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29910,7 +29901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A738" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29950,7 +29941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="739" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A739" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -29990,7 +29981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A740" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30030,7 +30021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="741" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A741" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30070,7 +30061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="742" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A742" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30110,7 +30101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="743" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A743" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30150,7 +30141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="744" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A744" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30190,7 +30181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="745" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A745" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30230,7 +30221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A746" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30270,7 +30261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A747" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30310,7 +30301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="748" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A748" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30350,7 +30341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A749" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30390,7 +30381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A750" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30430,7 +30421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A751" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30470,7 +30461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A752" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30510,7 +30501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="753" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A753" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30550,7 +30541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="754" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A754" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30590,7 +30581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A755" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30630,7 +30621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="756" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A756" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30670,7 +30661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="757" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A757" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30709,7 +30700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="758" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A758" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30749,7 +30740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="759" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A759" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30789,7 +30780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="760" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A760" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30829,7 +30820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="761" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A761" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30869,7 +30860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A762" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30909,7 +30900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="763" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A763" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30949,7 +30940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="764" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A764" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -30989,7 +30980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="765" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A765" t="str">
         <f t="shared" si="976"/>
         <v>r08</v>
@@ -31029,7 +31020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A766" t="str">
         <f t="shared" ref="A766:A829" si="1057">A765</f>
         <v>r08</v>
@@ -31069,7 +31060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="767" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A767" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31109,7 +31100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A768" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31149,7 +31140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="769" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A769" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31189,7 +31180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="770" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A770" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31229,7 +31220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A771" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31269,7 +31260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="772" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A772" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31309,7 +31300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="773" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A773" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31349,7 +31340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="774" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A774" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31389,7 +31380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A775" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31429,7 +31420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="776" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A776" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31469,7 +31460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="777" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A777" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31509,7 +31500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="778" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A778" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31549,7 +31540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A779" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31589,7 +31580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A780" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31629,7 +31620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="781" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A781" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31669,7 +31660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="782" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A782" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31709,7 +31700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="783" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A783" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31749,7 +31740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="784" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A784" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31789,7 +31780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="785" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A785" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31829,7 +31820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A786" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31869,7 +31860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="787" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A787" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31909,7 +31900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="788" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A788" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31949,7 +31940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="789" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A789" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -31989,7 +31980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="790" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A790" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32029,7 +32020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="791" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A791" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32069,7 +32060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="792" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A792" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32109,7 +32100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="793" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A793" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32149,7 +32140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="794" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A794" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32189,7 +32180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="795" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A795" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32229,7 +32220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A796" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32269,7 +32260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="797" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A797" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32309,7 +32300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="798" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A798" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32349,7 +32340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="799" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A799" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32389,7 +32380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="800" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A800" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32429,7 +32420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="801" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A801" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32469,7 +32460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="802" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A802" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32509,7 +32500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="803" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A803" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32549,7 +32540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A804" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32589,7 +32580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="805" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A805" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32629,7 +32620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="806" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A806" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32669,7 +32660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A807" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32709,7 +32700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="808" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A808" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32749,7 +32740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="809" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A809" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32789,7 +32780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="810" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A810" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32829,7 +32820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="811" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A811" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32869,7 +32860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="812" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A812" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32909,7 +32900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A813" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32949,7 +32940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A814" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -32989,7 +32980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A815" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33029,7 +33020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="816" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A816" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33069,7 +33060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="817" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A817" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33109,7 +33100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="818" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A818" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33149,7 +33140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="819" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A819" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33189,7 +33180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="820" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A820" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33229,7 +33220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="821" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A821" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33269,7 +33260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="822" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A822" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33309,7 +33300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="823" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A823" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33349,7 +33340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="824" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A824" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33389,7 +33380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="825" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A825" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33429,7 +33420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="826" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A826" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33469,7 +33460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="827" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A827" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33509,7 +33500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="828" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A828" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33549,7 +33540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="829" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A829" t="str">
         <f t="shared" si="1057"/>
         <v>r08</v>
@@ -33589,7 +33580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="830" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A830" t="str">
         <f t="shared" ref="A830:A888" si="1176">A829</f>
         <v>r08</v>
@@ -33629,7 +33620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="831" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A831" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33669,7 +33660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="832" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A832" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33709,7 +33700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="833" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A833" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33749,7 +33740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A834" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33789,7 +33780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="835" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A835" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33829,7 +33820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="836" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A836" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33869,7 +33860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A837" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33909,7 +33900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="838" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A838" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33949,7 +33940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="839" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A839" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -33989,7 +33980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="840" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A840" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34028,7 +34019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="841" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A841" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34068,7 +34059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="842" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A842" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34108,7 +34099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="843" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A843" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34148,7 +34139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="844" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A844" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34188,7 +34179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="845" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A845" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34228,7 +34219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="846" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A846" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34268,7 +34259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="847" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A847" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34308,7 +34299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="848" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A848" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34348,7 +34339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A849" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34388,7 +34379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="850" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A850" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34428,7 +34419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="851" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A851" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34468,7 +34459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="852" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A852" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34508,7 +34499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="853" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A853" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34548,7 +34539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="854" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A854" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34588,7 +34579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="855" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A855" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34628,7 +34619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="856" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A856" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34668,7 +34659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A857" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34708,7 +34699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="858" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A858" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34748,7 +34739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="859" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A859" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34788,7 +34779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A860" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34828,7 +34819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A861" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34868,7 +34859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="862" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A862" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34908,7 +34899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="863" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A863" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34948,7 +34939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="864" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A864" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -34988,7 +34979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A865" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35028,7 +35019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="866" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A866" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35068,7 +35059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="867" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A867" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35108,7 +35099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="868" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A868" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35148,7 +35139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A869" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35188,7 +35179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="870" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A870" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35228,7 +35219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="871" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A871" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35268,7 +35259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="872" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A872" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35308,7 +35299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="873" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A873" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35348,7 +35339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="874" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A874" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35388,7 +35379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="875" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A875" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35428,7 +35419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="876" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A876" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35468,7 +35459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="877" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A877" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35508,7 +35499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="878" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A878" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35548,7 +35539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="879" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A879" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35588,7 +35579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="880" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A880" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35628,7 +35619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="881" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A881" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35668,7 +35659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="882" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A882" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35708,7 +35699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="883" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A883" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35748,7 +35739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="884" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A884" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35788,7 +35779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="885" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A885" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35828,7 +35819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="886" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A886" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35868,7 +35859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="887" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A887" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35908,7 +35899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="888" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A888" t="str">
         <f t="shared" si="1176"/>
         <v>r08</v>
@@ -35948,7 +35939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="889" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A889" t="s">
         <v>24</v>
       </c>
@@ -35983,7 +35974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="890" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A890" t="str">
         <f>A889</f>
         <v>r09</v>
@@ -36025,7 +36016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="891" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A891" t="str">
         <f t="shared" ref="A891:A954" si="1270">A890</f>
         <v>r09</v>
@@ -36067,7 +36058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="892" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A892" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36109,7 +36100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="893" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A893" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36151,7 +36142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="894" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A894" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36194,7 +36185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="895" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A895" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36237,7 +36228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="896" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A896" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36280,7 +36271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="897" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A897" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36323,7 +36314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="898" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A898" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36367,7 +36358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="899" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A899" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36411,7 +36402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="900" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A900" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36455,7 +36446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="901" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A901" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36497,7 +36488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="902" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A902" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36540,7 +36531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="903" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A903" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36583,7 +36574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="904" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A904" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36626,7 +36617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="905" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A905" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36669,7 +36660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="906" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A906" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36712,7 +36703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A907" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36755,7 +36746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="908" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A908" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36798,7 +36789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="909" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A909" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36841,7 +36832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="910" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A910" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36884,7 +36875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="911" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A911" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36927,7 +36918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A912" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -36970,7 +36961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="913" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A913" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37013,7 +37004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="914" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A914" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37057,7 +37048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="915" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A915" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37101,7 +37092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="916" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A916" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37145,7 +37136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="917" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A917" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37189,7 +37180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="918" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A918" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37233,7 +37224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="919" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A919" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37277,7 +37268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="920" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A920" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37321,7 +37312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="921" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A921" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37365,7 +37356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="922" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A922" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37409,7 +37400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="923" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A923" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37453,7 +37444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="924" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A924" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37497,7 +37488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="925" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A925" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37541,7 +37532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="926" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A926" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37585,7 +37576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="927" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A927" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37627,7 +37618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="928" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A928" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37669,7 +37660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="929" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A929" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37712,7 +37703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="930" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A930" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37755,7 +37746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="931" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A931" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37798,7 +37789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="932" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A932" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37842,7 +37833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="933" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A933" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37886,7 +37877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="934" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A934" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37930,7 +37921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="935" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A935" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -37974,7 +37965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="936" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A936" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38018,7 +38009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="937" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A937" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38059,7 +38050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="938" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A938" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38100,7 +38091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="939" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A939" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38141,7 +38132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="940" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A940" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38182,7 +38173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="941" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A941" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38223,7 +38214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="942" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A942" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38264,7 +38255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="943" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A943" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38305,7 +38296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="944" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A944" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38346,7 +38337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="945" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A945" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38387,7 +38378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="946" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A946" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38428,7 +38419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="947" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A947" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38469,7 +38460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="948" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A948" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38510,7 +38501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="949" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A949" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38551,7 +38542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="950" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A950" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38592,7 +38583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="951" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A951" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38633,7 +38624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="952" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A952" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38674,7 +38665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="953" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A953" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38714,7 +38705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="954" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A954" t="str">
         <f t="shared" si="1270"/>
         <v>r09</v>
@@ -38754,7 +38745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="955" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A955" t="str">
         <f t="shared" ref="A955:A1018" si="1381">A954</f>
         <v>r09</v>
@@ -38794,7 +38785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="956" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A956" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -38834,7 +38825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="957" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A957" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -38874,7 +38865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="958" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A958" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -38914,7 +38905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="959" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A959" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -38954,7 +38945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="960" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A960" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -38994,7 +38985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="961" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A961" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39034,7 +39025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="962" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A962" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39074,7 +39065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="963" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A963" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39114,7 +39105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="964" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A964" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39154,7 +39145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="965" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A965" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39194,7 +39185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="966" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A966" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39234,7 +39225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="967" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A967" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39274,7 +39265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="968" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A968" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39314,7 +39305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="969" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A969" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39360,7 +39351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="970" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A970" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39406,7 +39397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="971" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A971" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39452,7 +39443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="972" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A972" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39498,7 +39489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="973" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A973" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39544,7 +39535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="974" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A974" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39590,7 +39581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="975" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A975" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39636,7 +39627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="976" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A976" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39682,7 +39673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="977" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A977" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39722,7 +39713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="978" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A978" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39762,7 +39753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="979" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A979" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39802,7 +39793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="980" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A980" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39842,7 +39833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="981" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A981" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39887,7 +39878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="982" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A982" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39933,7 +39924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="983" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A983" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -39979,7 +39970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="984" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A984" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40025,7 +40016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="985" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A985" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40071,7 +40062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="986" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A986" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40117,7 +40108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="987" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A987" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40163,7 +40154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="988" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A988" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40209,7 +40200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="989" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A989" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40255,7 +40246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="990" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A990" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40301,7 +40292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="991" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A991" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40347,7 +40338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="992" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A992" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40393,7 +40384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="993" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40433,7 +40424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="994" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A994" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40473,7 +40464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="995" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40513,7 +40504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="996" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40553,7 +40544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="997" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40599,7 +40590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="998" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40645,7 +40636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="999" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A999" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40691,7 +40682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1000" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1000" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40737,7 +40728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1001" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1001" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40783,7 +40774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1002" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1002" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40829,7 +40820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1003" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1003" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40875,7 +40866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1004" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1004" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40921,7 +40912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1005" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1005" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -40967,7 +40958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1006" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1006" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41013,7 +41004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1007" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1007" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41059,7 +41050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1008" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1008" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41105,7 +41096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1009" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1009" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41145,7 +41136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1010" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1010" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41185,7 +41176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1011" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41225,7 +41216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1012" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1012" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41265,7 +41256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1013" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1013" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41311,7 +41302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1014" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1014" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41357,7 +41348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1015" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1015" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41403,7 +41394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1016" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1016" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41449,7 +41440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1017" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1017" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41495,7 +41486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1018" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1018" t="str">
         <f t="shared" si="1381"/>
         <v>r09</v>
@@ -41541,7 +41532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1019" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1019" t="str">
         <f t="shared" ref="A1019:A1082" si="1521">A1018</f>
         <v>r09</v>
@@ -41587,7 +41578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1020" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1020" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41633,7 +41624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1021" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1021" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41679,7 +41670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1022" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1022" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41725,7 +41716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1023" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1023" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41771,7 +41762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1024" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1024" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41817,7 +41808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1025" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1025" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41857,7 +41848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1026" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1026" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41897,7 +41888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1027" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1027" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41937,7 +41928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1028" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1028" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -41977,7 +41968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1029" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1029" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42023,7 +42014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1030" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1030" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42069,7 +42060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1031" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1031" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42115,7 +42106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1032" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1032" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1032" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42161,7 +42152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1033" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1033" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42207,7 +42198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1034" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1034" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1034" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42253,7 +42244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1035" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1035" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1035" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42299,7 +42290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1036" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1036" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1036" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42345,7 +42336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1037" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1037" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1037" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42391,7 +42382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1038" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1038" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1038" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42437,7 +42428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1039" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1039" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1039" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42483,7 +42474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1040" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1040" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1040" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42529,7 +42520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1041" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1041" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1041" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42569,7 +42560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1042" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1042" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1042" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42609,7 +42600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1043" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1043" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1043" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42649,7 +42640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1044" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1044" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1044" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42689,7 +42680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1045" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1045" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1045" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42735,7 +42726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1046" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1046" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1046" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42781,7 +42772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1047" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1047" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1047" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42827,7 +42818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1048" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1048" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1048" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42873,7 +42864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1049" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1049" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1049" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42919,7 +42910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1050" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1050" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1050" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -42965,7 +42956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1051" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1051" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1051" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43011,7 +43002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1052" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1052" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1052" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43057,7 +43048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1053" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1053" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1053" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43103,7 +43094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1054" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1054" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1054" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43149,7 +43140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1055" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1055" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1055" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43195,7 +43186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1056" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1056" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1056" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43241,7 +43232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1057" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1057" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1057" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43281,7 +43272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1058" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1058" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1058" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43321,7 +43312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1059" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1059" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1059" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43361,7 +43352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1060" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1060" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1060" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43401,7 +43392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1061" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1061" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1061" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43447,7 +43438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1062" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1062" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1062" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43493,7 +43484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1063" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1063" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1063" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43539,7 +43530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1064" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1064" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1064" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43585,7 +43576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1065" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1065" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1065" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43631,7 +43622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1066" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1066" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1066" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43677,7 +43668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1067" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1067" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1067" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43723,7 +43714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1068" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1068" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1068" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43769,7 +43760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1069" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1069" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1069" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43815,7 +43806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1070" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1070" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1070" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43861,7 +43852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1071" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1071" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1071" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43907,7 +43898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1072" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1072" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1072" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43953,7 +43944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1073" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1073" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1073" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -43993,7 +43984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1074" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1074" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1074" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44033,7 +44024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1075" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1075" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1075" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44073,7 +44064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1076" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1076" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1076" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44113,7 +44104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1077" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1077" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1077" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44159,7 +44150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1078" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1078" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1078" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44205,7 +44196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1079" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1079" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1079" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44251,7 +44242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1080" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1080" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1080" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44297,7 +44288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1081" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1081" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1081" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44343,7 +44334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1082" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1082" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1082" t="str">
         <f t="shared" si="1521"/>
         <v>r09</v>
@@ -44389,7 +44380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1083" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1083" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1083" t="str">
         <f t="shared" ref="A1083:A1128" si="1654">A1082</f>
         <v>r09</v>
@@ -44435,7 +44426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1084" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1084" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1084" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44481,7 +44472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1085" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1085" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1085" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44527,7 +44518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1086" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1086" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1086" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44573,7 +44564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1087" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1087" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1087" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44619,7 +44610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1088" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1088" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1088" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44665,7 +44656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1089" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1089" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1089" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44705,7 +44696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1090" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1090" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1090" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44745,7 +44736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1091" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1091" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1091" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44785,7 +44776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1092" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1092" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1092" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44825,7 +44816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1093" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1093" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1093" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44871,7 +44862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1094" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1094" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1094" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44917,7 +44908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1095" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1095" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1095" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -44963,7 +44954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1096" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1096" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1096" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45009,7 +45000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1097" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1097" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1097" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45055,7 +45046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1098" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1098" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1098" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45101,7 +45092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1099" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1099" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1099" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45147,7 +45138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1100" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45193,7 +45184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1101" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1101" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45239,7 +45230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1102" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1102" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45285,7 +45276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1103" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45331,7 +45322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1104" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45377,7 +45368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1105" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45417,7 +45408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1106" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1106" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45457,7 +45448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1107" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45497,7 +45488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1108" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45537,7 +45528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1109" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1109" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45583,7 +45574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1110" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1110" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45629,7 +45620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1111" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45675,7 +45666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1112" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45721,7 +45712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1113" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45767,7 +45758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1114" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45813,7 +45804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1115" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45859,7 +45850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1116" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45905,7 +45896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1117" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1117" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45951,7 +45942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1118" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1118" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -45997,7 +45988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1119" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46043,7 +46034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1120" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46089,7 +46080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1121" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46129,7 +46120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1122" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46169,7 +46160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1123" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46215,7 +46206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1124" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46261,7 +46252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1125" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46307,7 +46298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1126" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46353,7 +46344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1127" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1127" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46399,7 +46390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1128" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="1128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1128" t="str">
         <f t="shared" si="1654"/>
         <v>r09</v>
@@ -46446,18 +46437,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1128" xr:uid="{9EE4B7C3-6EEC-3E40-A639-037475DFAEB6}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="r07"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="ci216"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K1128" xr:uid="{9EE4B7C3-6EEC-3E40-A639-037475DFAEB6}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
